--- a/static/data/exports/Retro_HP_GE_2014.xlsx
+++ b/static/data/exports/Retro_HP_GE_2014.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="Q2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>21</v>
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="Q25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
         <v>21</v>
@@ -2809,7 +2809,7 @@
         </is>
       </c>
       <c r="Q38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
         <v>21</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Q51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
         <v>21</v>
@@ -4421,7 +4421,7 @@
         </is>
       </c>
       <c r="Q64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
         <v>21</v>
@@ -5227,7 +5227,7 @@
         </is>
       </c>
       <c r="Q77" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
         <v>21</v>
@@ -6033,7 +6033,7 @@
         </is>
       </c>
       <c r="Q90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R90" t="n">
         <v>21</v>
@@ -6839,7 +6839,7 @@
         </is>
       </c>
       <c r="Q103" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R103" t="n">
         <v>21</v>
@@ -9009,7 +9009,7 @@
         </is>
       </c>
       <c r="Q138" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R138" t="n">
         <v>21</v>
@@ -9815,7 +9815,7 @@
         </is>
       </c>
       <c r="Q151" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R151" t="n">
         <v>21</v>
@@ -10621,7 +10621,7 @@
         </is>
       </c>
       <c r="Q164" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R164" t="n">
         <v>21</v>
@@ -11427,7 +11427,7 @@
         </is>
       </c>
       <c r="Q177" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R177" t="n">
         <v>21</v>
@@ -12233,7 +12233,7 @@
         </is>
       </c>
       <c r="Q190" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R190" t="n">
         <v>21</v>
@@ -13039,7 +13039,7 @@
         </is>
       </c>
       <c r="Q203" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R203" t="n">
         <v>21</v>
@@ -13845,7 +13845,7 @@
         </is>
       </c>
       <c r="Q216" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R216" t="n">
         <v>21</v>
@@ -14651,7 +14651,7 @@
         </is>
       </c>
       <c r="Q229" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R229" t="n">
         <v>21</v>
@@ -15457,7 +15457,7 @@
         </is>
       </c>
       <c r="Q242" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R242" t="n">
         <v>21</v>

--- a/static/data/exports/Retro_HP_GE_2014.xlsx
+++ b/static/data/exports/Retro_HP_GE_2014.xlsx
@@ -1470,11 +1470,11 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E17" t="n">
         <v>411</v>
@@ -4189,20 +4189,20 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>1506284</v>
+        <v>1506285</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>BALDEV RAJ</t>
+          <t>DR. ATUL THAKUR BHARMORI</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>HiSP</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>16543</v>
+        <v>16536</v>
       </c>
       <c r="E61" t="n">
         <v>72</v>
@@ -4226,12 +4226,12 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>BALDEV RAJ</t>
+          <t>DR. ATUL THAKUR BHARMORI</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>HiSP</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="Q61" t="b">
@@ -4251,20 +4251,20 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>1506285</v>
+        <v>1506284</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>DR. ATUL THAKUR BHARMORI</t>
+          <t>BALDEV RAJ</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>HiSP</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>16536</v>
+        <v>16543</v>
       </c>
       <c r="E62" t="n">
         <v>72</v>
@@ -4288,12 +4288,12 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>DR. ATUL THAKUR BHARMORI</t>
+          <t>BALDEV RAJ</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>HiSP</t>
         </is>
       </c>
       <c r="Q62" t="b">
@@ -11133,20 +11133,20 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>1506827</v>
+        <v>1506826</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>DHANI RAM</t>
+          <t>BALDEV RAJ</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>HiSP</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>16536</v>
+        <v>16543</v>
       </c>
       <c r="E173" t="n">
         <v>55</v>
@@ -11170,12 +11170,12 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>DHANI RAM</t>
+          <t>BALDEV RAJ</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>HiSP</t>
         </is>
       </c>
       <c r="Q173" t="b">
@@ -11195,20 +11195,20 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>1506826</v>
+        <v>1506827</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>BALDEV RAJ</t>
+          <t>DHANI RAM</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>HiSP</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>16543</v>
+        <v>16536</v>
       </c>
       <c r="E174" t="n">
         <v>55</v>
@@ -11232,12 +11232,12 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>BALDEV RAJ</t>
+          <t>DHANI RAM</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>HiSP</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="Q174" t="b">
@@ -12869,20 +12869,20 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>1506950</v>
+        <v>1506949</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>BALDEV RAJ</t>
+          <t>RAMAN KUMAR</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>HiSP</t>
+          <t>BMUP</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>16543</v>
+        <v>16544</v>
       </c>
       <c r="E201" t="n">
         <v>42</v>
@@ -12906,12 +12906,12 @@
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>BALDEV RAJ</t>
+          <t>RAMAN KUMAR</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>HiSP</t>
+          <t>BMUP</t>
         </is>
       </c>
       <c r="Q201" t="b">
@@ -12931,20 +12931,20 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>1506949</v>
+        <v>1506950</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>RAMAN KUMAR</t>
+          <t>BALDEV RAJ</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>BMUP</t>
+          <t>HiSP</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>16544</v>
+        <v>16543</v>
       </c>
       <c r="E202" t="n">
         <v>42</v>
@@ -12968,12 +12968,12 @@
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>RAMAN KUMAR</t>
+          <t>BALDEV RAJ</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>BMUP</t>
+          <t>HiSP</t>
         </is>
       </c>
       <c r="Q202" t="b">
@@ -15163,20 +15163,20 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>1507148</v>
+        <v>1507149</v>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>BALDEV RAJ</t>
+          <t>DHANI RAM</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>HiSP</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D238" t="n">
-        <v>16543</v>
+        <v>16536</v>
       </c>
       <c r="E238" t="n">
         <v>62</v>
@@ -15200,12 +15200,12 @@
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t>BALDEV RAJ</t>
+          <t>DHANI RAM</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t>HiSP</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="Q238" t="b">
@@ -15225,20 +15225,20 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>1507149</v>
+        <v>1507148</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>DHANI RAM</t>
+          <t>BALDEV RAJ</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>HiSP</t>
         </is>
       </c>
       <c r="D239" t="n">
-        <v>16536</v>
+        <v>16543</v>
       </c>
       <c r="E239" t="n">
         <v>62</v>
@@ -15262,12 +15262,12 @@
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t>DHANI RAM</t>
+          <t>BALDEV RAJ</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>HiSP</t>
         </is>
       </c>
       <c r="Q239" t="b">
@@ -16350,11 +16350,11 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D257" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E257" t="n">
         <v>168</v>
@@ -17032,11 +17032,11 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D268" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E268" t="n">
         <v>621</v>
@@ -17652,11 +17652,11 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D278" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E278" t="n">
         <v>684</v>
@@ -18210,11 +18210,11 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D287" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E287" t="n">
         <v>1001</v>
@@ -18830,11 +18830,11 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D297" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E297" t="n">
         <v>1966</v>
@@ -19512,11 +19512,11 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D308" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E308" t="n">
         <v>509</v>
@@ -20132,11 +20132,11 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D318" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E318" t="n">
         <v>546</v>
@@ -20690,11 +20690,11 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D327" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E327" t="n">
         <v>639</v>
@@ -21310,11 +21310,11 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D337" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E337" t="n">
         <v>970</v>
@@ -21930,11 +21930,11 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D347" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E347" t="n">
         <v>730</v>
@@ -22550,11 +22550,11 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D357" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E357" t="n">
         <v>2135</v>
@@ -23914,11 +23914,11 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D379" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E379" t="n">
         <v>661</v>
@@ -24472,11 +24472,11 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D388" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E388" t="n">
         <v>595</v>
@@ -25092,11 +25092,11 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D398" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E398" t="n">
         <v>792</v>
@@ -35260,11 +35260,11 @@
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D562" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E562" t="n">
         <v>1429</v>
@@ -36066,11 +36066,11 @@
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D575" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E575" t="n">
         <v>278</v>
@@ -36562,11 +36562,11 @@
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D583" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E583" t="n">
         <v>152</v>
@@ -36934,11 +36934,11 @@
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D589" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E589" t="n">
         <v>377</v>
@@ -37430,11 +37430,11 @@
       </c>
       <c r="C597" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D597" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E597" t="n">
         <v>214</v>
@@ -37802,11 +37802,11 @@
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D603" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E603" t="n">
         <v>469</v>
@@ -38422,11 +38422,11 @@
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D613" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E613" t="n">
         <v>443</v>
@@ -38732,11 +38732,11 @@
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D618" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E618" t="n">
         <v>682</v>
@@ -39414,11 +39414,11 @@
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D629" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E629" t="n">
         <v>509</v>
@@ -39724,11 +39724,11 @@
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D634" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E634" t="n">
         <v>554</v>
@@ -40530,11 +40530,11 @@
       </c>
       <c r="C647" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D647" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E647" t="n">
         <v>211</v>
@@ -40716,11 +40716,11 @@
       </c>
       <c r="C650" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D650" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E650" t="n">
         <v>1492</v>
@@ -41274,11 +41274,11 @@
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D659" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E659" t="n">
         <v>983</v>
@@ -41770,11 +41770,11 @@
       </c>
       <c r="C667" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D667" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E667" t="n">
         <v>1473</v>
@@ -42266,11 +42266,11 @@
       </c>
       <c r="C675" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D675" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E675" t="n">
         <v>413</v>
@@ -42700,11 +42700,11 @@
       </c>
       <c r="C682" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D682" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E682" t="n">
         <v>608</v>
@@ -43196,11 +43196,11 @@
       </c>
       <c r="C690" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D690" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E690" t="n">
         <v>1213</v>
@@ -43816,11 +43816,11 @@
       </c>
       <c r="C700" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D700" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E700" t="n">
         <v>1140</v>
@@ -44374,11 +44374,11 @@
       </c>
       <c r="C709" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D709" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E709" t="n">
         <v>314</v>
